--- a/config/reskillable/расчёты.xlsx
+++ b/config/reskillable/расчёты.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Minecraft\profiles\TechnoVanilla 1.1.4\config\reskillable\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76121DFD-D9C8-45DC-88D0-0F06B6E7CCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E75B5C78-4ACF-4AC3-A955-0A88F11B940A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -419,17 +419,17 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" s="1">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1">
         <v>3</v>
       </c>
       <c r="D3" s="1">
         <f>(A3*B3)-4+(C3*2)</f>
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -458,17 +458,17 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D7" s="1">
         <f>(A7+B7)*1</f>
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
@@ -477,7 +477,7 @@
       </c>
       <c r="D8" s="1">
         <f>(A7+B7)*2</f>
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
@@ -486,7 +486,7 @@
       </c>
       <c r="D9" s="1">
         <f>(A7+B7)*3</f>
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -495,7 +495,7 @@
       </c>
       <c r="D10" s="1">
         <f>(A7+B7)*4</f>
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
